--- a/business_surveys/039_institutional_knowledge_sharing_culture_survey--business_surveys.xlsx
+++ b/business_surveys/039_institutional_knowledge_sharing_culture_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high',_'value':_5}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High', 'value': 5}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_4}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 4}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_2}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 2}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_low',_'value':_1}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low', 'value': 1}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_high',_'value':_5}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very High', 'value': 5}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_4}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 4}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_2}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 2}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_low',_'value':_1}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low', 'value': 1}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'regularly',_'value':_'regularly'}</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Regularly', 'value': 'Regularly'}</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_high',_'value':_5}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very High', 'value': 5}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_4}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 4}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_3}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 3}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_2}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 2}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'very_low',_'value':_1}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low', 'value': 1}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'very_high',_'value':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Very High', 'value': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'very_low',_'value':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low', 'value': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'very_important',_'value':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Very Important', 'value': 'Very Important'}</t>
+          <t>Very Important</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_important',_'value':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Important', 'value': 'Somewhat Important'}</t>
+          <t>Somewhat Important</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_important',_'value':_'not_very_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Not Very Important', 'value': 'Not Very Important'}</t>
+          <t>Not Very Important</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_important',_'value':_'not_at_all_important'}</t>
+          <t>not_at_all_important</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Not At All Important', 'value': 'Not At All Important'}</t>
+          <t>Not At All Important</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'language',_'value':_'language'}</t>
+          <t>language</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Language', 'value': 'Language'}</t>
+          <t>Language</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'cultural',_'value':_'cultural'}</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Cultural', 'value': 'Cultural'}</t>
+          <t>Cultural</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'fear',_'value':_'fear'}</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Fear', 'value': 'Fear'}</t>
+          <t>Fear</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
